--- a/data.mn/public/datasets/unemployment-rate-by-location.xlsx
+++ b/data.mn/public/datasets/unemployment-rate-by-location.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,11 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,22 +424,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Rural</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Ulaanbaatar</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
@@ -686,6 +681,286 @@
       </c>
       <c r="D18" t="n">
         <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>он</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Улаанбаатар</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Хот</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Хөдөө</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B9" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
